--- a/upload/Титан запрос Заколодний Роман.xlsx
+++ b/upload/Титан запрос Заколодний Роман.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="БРОЗЭКС, Рыгалов" sheetId="1" r:id="rId1"/>
+    <sheet name="БРОЗЭКС" sheetId="1" r:id="rId1"/>
     <sheet name="Рыгалов С.В." sheetId="3" r:id="rId2"/>
     <sheet name="Общий по точкам" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -787,7 +787,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,9 +801,9 @@
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="95.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
